--- a/Config/Excel/LevelTypeConfig.xlsx
+++ b/Config/Excel/LevelTypeConfig.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$6</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Id</t>
   </si>
@@ -65,6 +65,12 @@
   </si>
   <si>
     <t>Boss</t>
+  </si>
+  <si>
+    <t>精英怪</t>
+  </si>
+  <si>
+    <t>Elite</t>
   </si>
 </sst>
 </file>
@@ -998,8 +1004,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5" outlineLevelCol="2"/>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="6" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="20.8888888888889" customWidth="1"/>
     <col min="2" max="2" width="24.4444444444444" customWidth="1"/>
@@ -1059,8 +1065,19 @@
         <v>9</v>
       </c>
     </row>
+    <row r="7" spans="1:3">
+      <c r="A7">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:B2" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:B6" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
